--- a/Employee_Reports_wi52/Joe Peter Angustia Pimentel Q0618.xlsx
+++ b/Employee_Reports_wi52/Joe Peter Angustia Pimentel Q0618.xlsx
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K35"/>
+  <dimension ref="A1:K36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -569,11 +569,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>426</v>
+        <v>418</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -618,11 +618,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>427</v>
+        <v>419</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -667,11 +667,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>426</v>
+        <v>418</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -716,11 +716,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>427</v>
+        <v>419</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -765,11 +765,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -814,11 +814,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>427</v>
+        <v>419</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -863,11 +863,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -912,11 +912,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>427</v>
+        <v>419</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -961,11 +961,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1010,11 +1010,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>436</v>
+        <v>428</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1059,11 +1059,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>440</v>
+        <v>432</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1108,11 +1108,11 @@
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>432</v>
+        <v>424</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1157,11 +1157,11 @@
         </is>
       </c>
       <c r="H15" s="3" t="n">
-        <v>433</v>
+        <v>425</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1206,11 +1206,11 @@
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>440</v>
+        <v>432</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1255,11 +1255,11 @@
         </is>
       </c>
       <c r="H17" s="3" t="n">
-        <v>434</v>
+        <v>426</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1304,11 +1304,11 @@
         </is>
       </c>
       <c r="H18" s="3" t="n">
-        <v>433</v>
+        <v>425</v>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -1353,11 +1353,11 @@
         </is>
       </c>
       <c r="H19" s="3" t="n">
-        <v>433</v>
+        <v>425</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -1402,11 +1402,11 @@
         </is>
       </c>
       <c r="H20" s="3" t="n">
-        <v>434</v>
+        <v>426</v>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -1451,11 +1451,11 @@
         </is>
       </c>
       <c r="H21" s="3" t="n">
-        <v>504</v>
+        <v>496</v>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -1500,11 +1500,11 @@
         </is>
       </c>
       <c r="H22" s="3" t="n">
-        <v>505</v>
+        <v>497</v>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
@@ -1549,11 +1549,11 @@
         </is>
       </c>
       <c r="H23" s="3" t="n">
-        <v>471</v>
+        <v>463</v>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
@@ -1598,11 +1598,11 @@
         </is>
       </c>
       <c r="H24" s="3" t="n">
-        <v>505</v>
+        <v>497</v>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
@@ -1647,11 +1647,11 @@
         </is>
       </c>
       <c r="H25" s="3" t="n">
-        <v>435</v>
+        <v>427</v>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -1684,11 +1684,11 @@
         </is>
       </c>
       <c r="H26" s="3" t="n">
-        <v>429</v>
+        <v>421</v>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
@@ -1733,11 +1733,11 @@
         </is>
       </c>
       <c r="H27" s="3" t="n">
-        <v>504</v>
+        <v>496</v>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
@@ -1782,11 +1782,11 @@
         </is>
       </c>
       <c r="H28" s="3" t="n">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
@@ -1831,11 +1831,11 @@
         </is>
       </c>
       <c r="H29" s="3" t="n">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
@@ -1880,11 +1880,11 @@
         </is>
       </c>
       <c r="H30" s="3" t="n">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
@@ -1929,11 +1929,11 @@
         </is>
       </c>
       <c r="H31" s="3" t="n">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
@@ -1978,11 +1978,11 @@
         </is>
       </c>
       <c r="H32" s="3" t="n">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
@@ -2027,11 +2027,11 @@
         </is>
       </c>
       <c r="H33" s="3" t="n">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
@@ -2076,11 +2076,11 @@
         </is>
       </c>
       <c r="H34" s="3" t="n">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>BCP for QDF-ASRS And MHE Due To Equipment failure (Other Trainings)</t>
+          <t>IS0 55001 (Other Trainings)</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr"/>
@@ -2104,28 +2104,65 @@
       <c r="E35" s="3" t="inlineStr"/>
       <c r="F35" s="3" t="inlineStr">
         <is>
+          <t>24-Aug-2026</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>23-Aug-2028</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="n">
+        <v>726</v>
+      </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>BCP for QDF-ASRS And MHE Due To Equipment failure (Other Trainings)</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr"/>
+      <c r="D36" s="3" t="inlineStr"/>
+      <c r="E36" s="3" t="inlineStr"/>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
           <t>12-May-2026</t>
         </is>
       </c>
-      <c r="G35" s="3" t="inlineStr">
+      <c r="G36" s="3" t="inlineStr">
         <is>
           <t>11-May-2028</t>
         </is>
       </c>
-      <c r="H35" s="3" t="n">
-        <v>630</v>
-      </c>
-      <c r="I35" s="3" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J35" s="3" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="K35" s="3" t="inlineStr"/>
+      <c r="H36" s="3" t="n">
+        <v>622</v>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2141,7 +2178,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2261,17 +2298,17 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Order Picker</t>
+          <t>Stretch Wrapper</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>22-Feb-2026</t>
+          <t>19-Aug-2026</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>41.31%</t>
+          <t>32.76%</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -2292,17 +2329,17 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Bin Conveyor System</t>
+          <t>Order Picker</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>29-Jan-2026</t>
+          <t>22-Feb-2026</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>36.07%</t>
+          <t>41.31%</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -2323,17 +2360,17 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Pallet Conveyor System</t>
+          <t>Bin Conveyor System</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>21-Jan-2026</t>
+          <t>29-Jan-2026</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>53.84%</t>
+          <t>36.07%</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
@@ -2354,61 +2391,61 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
+          <t>Pallet Conveyor System</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>21-Jan-2026</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>53.84%</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>low percentage</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>This is a low mark, please retake the exam and improve your score. date is valid</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
           <t>Bin Hoist S-Type</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>20-Apr-2026</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>45.21%</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>low percentage</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>This is a low mark, please retake the exam and improve your score. date is valid</t>
         </is>
       </c>
-      <c r="G8" s="4" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>Low Lift Truck T30</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>28-Jun-2026</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>77.03%</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>Approved Score. date is valid</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="n"/>
+      <c r="G9" s="4" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
@@ -2416,61 +2453,61 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
+          <t>Low Lift Truck T30</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>28-Jun-2026</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>77.03%</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Approved Score. date is valid</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
           <t>Bizerba Weight</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>27-Apr-2026</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>89.33%</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
         <is>
           <t>Approved Score. date is valid</t>
         </is>
       </c>
-      <c r="G10" s="3" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>Asrs Stacker Crane</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>21-Jul-2026</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>65.82%</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>low percentage</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>This is a low mark, please retake the exam and improve your score. date is valid</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="n"/>
+      <c r="G11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
@@ -2478,47 +2515,78 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
+          <t>Asrs Stacker Crane</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>21-Jul-2026</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>65.82%</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>low percentage</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>This is a low mark, please retake the exam and improve your score. date is valid</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
           <t>Pallet Hoist</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>09-Feb-2026</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>32.91%</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>low percentage</t>
         </is>
       </c>
-      <c r="F12" s="4" t="inlineStr">
+      <c r="F13" s="4" t="inlineStr">
         <is>
           <t>This is a low mark, please retake the exam and improve your score. date is valid</t>
         </is>
       </c>
-      <c r="G12" s="4" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr"/>
-      <c r="B13" s="3" t="inlineStr"/>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="G13" s="4" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr"/>
+      <c r="B14" s="3" t="inlineStr"/>
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>TOTAL AVERAGE</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>57.04%</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr"/>
-      <c r="F13" s="3" t="inlineStr"/>
-      <c r="G13" s="3" t="n"/>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>54.83%</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr"/>
+      <c r="F14" s="3" t="inlineStr"/>
+      <c r="G14" s="3" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
